--- a/EKG_Kalite_Yönetim_Sistemi/06_Garanti Sorunları Yönetimi/01_WIM1 - Koordinatör, Portal ve İade Parça/EKG-KLT-PNO-02_garanti_gostergeleri_ve_is_istasyonu_uyari_panosu.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/06_Garanti Sorunları Yönetimi/01_WIM1 - Koordinatör, Portal ve İade Parça/EKG-KLT-PNO-02_garanti_gostergeleri_ve_is_istasyonu_uyari_panosu.xlsx
@@ -1040,7 +1040,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-PNO-02&amp;C&amp;"Arial,Regular"&amp;11Garanti Göstergeleri ve İş İstasyonu Uyarı Panosu</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 10.06.2026 | Revizyon: 21.09.2026
+Revizyon nedeni: Tekil talep, kapanış süresi ve olay/istasyon aksiyonlarıyla hesaplanabilir garanti panosu kuruldu.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -1270,7 +1271,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-PNO-02&amp;C&amp;"Arial,Regular"&amp;11Garanti Göstergeleri ve İş İstasyonu Uyarı Panosu</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 10.06.2026 | Revizyon: 21.09.2026
+Revizyon nedeni: Tekil talep, kapanış süresi ve olay/istasyon aksiyonlarıyla hesaplanabilir garanti panosu kuruldu.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>